--- a/Employee_Reports_wi52/Kusal Sharmila Hewa Kokawalage Q0581.xlsx
+++ b/Employee_Reports_wi52/Kusal Sharmila Hewa Kokawalage Q0581.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-98</v>
+        <v>-106</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-90</v>
+        <v>-98</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-99</v>
+        <v>-107</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-440</v>
+        <v>-448</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-463</v>
+        <v>-471</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-53</v>
+        <v>-61</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1611,41 +1611,41 @@
       <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2024</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2026</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1670,11 +1670,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
